--- a/data/employees/EMP004/AST-EMP004-06.xlsx
+++ b/data/employees/EMP004/AST-EMP004-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Budget Tracker - Morgan Smith (Finance)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Morgan Smith | Role: Analyst | Location: Hsinchu | Date: 2025-01-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>72</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>67</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Cost Centre</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Budget ($K)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Actual ($K)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Variance ($K)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Variance %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CC-1001 Engineering</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2380</v>
-      </c>
-      <c r="D5" t="n">
-        <v>120</v>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>4.8</v>
+        <v>95</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Customer escalation analysis. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CC-1002 Operations</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1920</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-120</v>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>-6.7</v>
+        <v>88</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Section 1: Fabric semantic model planning. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CC-1003 R&amp;D</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3200</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3100</v>
-      </c>
-      <c r="D7" t="n">
-        <v>100</v>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>3.1</v>
+        <v>62</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Automation backlog refinement. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CC-1004 IT</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1195</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4</v>
+        <v>65</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>Section 1: Department KPI performance. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>71</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>91</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>91</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>87</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>66</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>77</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>86</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>61</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>77</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>94</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>68</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>79</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>76</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>62</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>60</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>92</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp004 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>75</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP004 contributes to ast emp004 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>